--- a/Output/Daily Scan_14 Jul 2026.xlsx
+++ b/Output/Daily Scan_14 Jul 2026.xlsx
@@ -509,7 +509,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>64.62</v>
+        <v>65.23</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -541,7 +541,7 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>38.66</v>
+        <v>35.93</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>67.7</v>
+        <v>62.48</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -605,11 +605,11 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>54.51</v>
+        <v>60.04</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &gt; 60</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -637,7 +637,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>48.23</v>
+        <v>54.78</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>53.54</v>
+        <v>50.05</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>45.99</v>
+        <v>51</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>54.05</v>
+        <v>54.61</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>75.65000000000001</v>
+        <v>72.59</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>45.71</v>
+        <v>49.27</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -829,11 +829,11 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>63.72</v>
+        <v>59.04</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -861,7 +861,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>65.73</v>
+        <v>60.64</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>55.28</v>
+        <v>47.86</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>51.43</v>
+        <v>50.08</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>47.29</v>
+        <v>45.06</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>76.23999999999999</v>
+        <v>68.53</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>56.89</v>
+        <v>51.9</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>65.29000000000001</v>
+        <v>61.28</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1085,11 +1085,11 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>42.28</v>
+        <v>38.8</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -1117,11 +1117,11 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>62.89</v>
+        <v>53.04</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -1149,7 +1149,7 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>51.18</v>
+        <v>47.3</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>45.7</v>
+        <v>44.15</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>46.99</v>
+        <v>46.51</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>60.12</v>
+        <v>60.53</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1277,11 +1277,11 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>66.93000000000001</v>
+        <v>58.63</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -1309,7 +1309,7 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>45.78</v>
+        <v>52.89</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>51.4</v>
+        <v>47.39</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>52.38</v>
+        <v>53.02</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>58.75</v>
+        <v>56.96</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>34.51</v>
+        <v>29.99</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>54.36</v>
+        <v>55.96</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>79.63</v>
+        <v>68.31</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>37.13</v>
+        <v>37.66</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>41.64</v>
+        <v>40.89</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>55.14</v>
+        <v>52.96</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>65.19</v>
+        <v>62.3</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>37.59</v>
+        <v>37.47</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1693,11 +1693,11 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>61.48</v>
+        <v>55.87</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -1725,7 +1725,7 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>53.36</v>
+        <v>51.1</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>38.19</v>
+        <v>35.66</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>51.77</v>
+        <v>46.83</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
-        <v>41.15</v>
+        <v>44.21</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -1853,11 +1853,11 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>45.03</v>
+        <v>39.19</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -1885,7 +1885,7 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
-        <v>33.64</v>
+        <v>30.52</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
-        <v>55.55</v>
+        <v>52.15</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
-        <v>61.96</v>
+        <v>62.61</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
-        <v>49.86</v>
+        <v>45.08</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
-        <v>39.23</v>
+        <v>36.92</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
-        <v>49.89</v>
+        <v>51.81</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
-        <v>52.65</v>
+        <v>54.07</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2141,11 +2141,11 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
-        <v>62.17</v>
+        <v>57.22</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -2173,7 +2173,7 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
-        <v>47.24</v>
+        <v>42.21</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
-        <v>78.45999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2237,11 +2237,11 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
-        <v>62.92</v>
+        <v>56.37</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -2269,7 +2269,7 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>54.86</v>
+        <v>48.52</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
-        <v>59.99</v>
+        <v>55.72</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
-        <v>51.93</v>
+        <v>45.97</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>54.85</v>
+        <v>46.51</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>44.92</v>
+        <v>41.1</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>47.36</v>
+        <v>43.6</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>47.56</v>
+        <v>45.45</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -2493,11 +2493,11 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>58.72</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &gt; 60</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -2525,7 +2525,7 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
-        <v>36.76</v>
+        <v>39.34</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>64.33</v>
+        <v>61.54</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
-        <v>40.56</v>
+        <v>53.97</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
-        <v>79.84</v>
+        <v>78.67</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
-        <v>59.24</v>
+        <v>57.5</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
-        <v>28.42</v>
+        <v>25.92</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
-        <v>52.14</v>
+        <v>50.74</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="n">
-        <v>39.24</v>
+        <v>38.63</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
-        <v>69.75</v>
+        <v>68.03</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -2813,11 +2813,11 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
-        <v>60.62</v>
+        <v>57.81</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -2845,11 +2845,11 @@
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
-        <v>40.57</v>
+        <v>38.79</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -2877,7 +2877,7 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
-        <v>53.14</v>
+        <v>51.03</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -2909,11 +2909,11 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
-        <v>60.81</v>
+        <v>52.78</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -2941,7 +2941,7 @@
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
-        <v>36.9</v>
+        <v>34.72</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
-        <v>35.51</v>
+        <v>33.36</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
-        <v>62.82</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -3037,11 +3037,11 @@
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
-        <v>36.41</v>
+        <v>40.19</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>RSI &lt; 40</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -3069,11 +3069,11 @@
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
-        <v>63.43</v>
+        <v>57.53</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -3101,7 +3101,7 @@
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
-        <v>43.18</v>
+        <v>41.7</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
-        <v>54</v>
+        <v>48.71</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
-        <v>51.24</v>
+        <v>45.08</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -3197,11 +3197,11 @@
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
-        <v>41.44</v>
+        <v>36.79</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -3229,7 +3229,7 @@
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="n">
-        <v>34.07</v>
+        <v>37.29</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="n">
-        <v>62.41</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
-        <v>45.31</v>
+        <v>45.98</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
-        <v>49.17</v>
+        <v>45.46</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -3357,11 +3357,11 @@
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
-        <v>54.61</v>
+        <v>61.19</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &gt; 60</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -3389,7 +3389,7 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
-        <v>39.33</v>
+        <v>35.81</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -3421,11 +3421,11 @@
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="n">
-        <v>60.38</v>
+        <v>58.08</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -3453,7 +3453,7 @@
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
-        <v>45.28</v>
+        <v>41.87</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
-        <v>70.15000000000001</v>
+        <v>66.61</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -3517,11 +3517,11 @@
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
-        <v>45.85</v>
+        <v>60.16</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &gt; 60</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -3549,7 +3549,7 @@
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
-        <v>44.76</v>
+        <v>44.51</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -3581,11 +3581,11 @@
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
-        <v>61.92</v>
+        <v>55.38</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -3613,7 +3613,7 @@
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
-        <v>64.05</v>
+        <v>63.4</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
-        <v>46.87</v>
+        <v>53.59</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
-        <v>67.69</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="n">
-        <v>59.45</v>
+        <v>56.09</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="n">
-        <v>58.76</v>
+        <v>52.53</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="n">
-        <v>48.49</v>
+        <v>45.68</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="n">
-        <v>50.61</v>
+        <v>50.95</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="n">
-        <v>66.70999999999999</v>
+        <v>63.81</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -3869,11 +3869,11 @@
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="n">
-        <v>61.2</v>
+        <v>58.75</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -3901,7 +3901,7 @@
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="n">
-        <v>47.21</v>
+        <v>47.47</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="n">
-        <v>62.61</v>
+        <v>71.13</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="n">
-        <v>40.68</v>
+        <v>40.36</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="n">
-        <v>65.63</v>
+        <v>69.91</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="n">
-        <v>55.89</v>
+        <v>51.67</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="n">
-        <v>56.4</v>
+        <v>51.15</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="n">
-        <v>48.35</v>
+        <v>51.66</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="n">
-        <v>50.8</v>
+        <v>47</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -4157,11 +4157,11 @@
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="n">
-        <v>61.12</v>
+        <v>57.75</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -4189,7 +4189,7 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="n">
-        <v>47.45</v>
+        <v>45.21</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
-        <v>44.59</v>
+        <v>42.05</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="n">
-        <v>59.93</v>
+        <v>50.25</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="n">
-        <v>31.92</v>
+        <v>32.74</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
-        <v>67.3</v>
+        <v>63.72</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -4349,11 +4349,11 @@
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="n">
-        <v>65.22</v>
+        <v>57.78</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -4381,11 +4381,11 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="n">
-        <v>64.2</v>
+        <v>56.91</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -4413,7 +4413,7 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="n">
-        <v>50.73</v>
+        <v>45.19</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="n">
-        <v>57.09</v>
+        <v>51.56</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="n">
-        <v>50.57</v>
+        <v>52.79</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="n">
-        <v>58.18</v>
+        <v>58.78</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -4541,11 +4541,11 @@
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="n">
-        <v>41.45</v>
+        <v>38.87</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -4573,11 +4573,11 @@
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="n">
-        <v>61.11</v>
+        <v>55.89</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -4605,7 +4605,7 @@
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="n">
-        <v>46.44</v>
+        <v>45.96</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="n">
-        <v>64.44</v>
+        <v>60.57</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="n">
-        <v>55.72</v>
+        <v>58.1</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="n">
-        <v>44.78</v>
+        <v>44.05</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="n">
-        <v>54.76</v>
+        <v>57.1</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="n">
-        <v>54.68</v>
+        <v>48.08</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="n">
-        <v>39.91</v>
+        <v>34.44</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="n">
-        <v>47.5</v>
+        <v>46.8</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="n">
-        <v>68.05</v>
+        <v>69.22</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="n">
-        <v>57.6</v>
+        <v>54.77</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -4925,11 +4925,11 @@
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="n">
-        <v>61.76</v>
+        <v>57.11</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -4957,7 +4957,7 @@
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="n">
-        <v>66.92</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="n">
-        <v>64.42</v>
+        <v>68.08</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="n">
-        <v>70.44</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="n">
-        <v>53.29</v>
+        <v>53.61</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -5085,11 +5085,11 @@
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="n">
-        <v>60.52</v>
+        <v>59.6</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -5117,7 +5117,7 @@
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="n">
-        <v>48.42</v>
+        <v>40.46</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="n">
-        <v>58.96</v>
+        <v>52.83</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="n">
-        <v>78.08</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="n">
-        <v>68.64</v>
+        <v>68.95</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="n">
-        <v>50.03</v>
+        <v>50.05</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="n">
-        <v>32.73</v>
+        <v>38.5</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="n">
-        <v>57.43</v>
+        <v>51.05</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="n">
-        <v>45.22</v>
+        <v>51.59</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="n">
-        <v>45.72</v>
+        <v>47.18</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="n">
-        <v>46.85</v>
+        <v>48.91</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="n">
-        <v>47.84</v>
+        <v>50.25</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="n">
-        <v>57.95</v>
+        <v>52.88</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="n">
-        <v>56.69</v>
+        <v>57.3</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="n">
-        <v>35.51</v>
+        <v>34.47</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="n">
-        <v>41.01</v>
+        <v>44.36</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="n">
-        <v>50.69</v>
+        <v>44.19</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="n">
-        <v>51.98</v>
+        <v>55.29</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="n">
-        <v>55.11</v>
+        <v>52.78</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="n">
-        <v>54.11</v>
+        <v>48.37</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -5725,11 +5725,11 @@
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="n">
-        <v>42</v>
+        <v>38.86</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -5757,7 +5757,7 @@
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="n">
-        <v>52.37</v>
+        <v>49.32</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="n">
-        <v>55.45</v>
+        <v>51.65</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -5821,11 +5821,11 @@
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="n">
-        <v>61.7</v>
+        <v>53.2</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -5853,7 +5853,7 @@
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="n">
-        <v>42.47</v>
+        <v>41.8</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="n">
-        <v>53</v>
+        <v>48.93</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="n">
-        <v>47.15</v>
+        <v>48.97</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="n">
-        <v>40.17</v>
+        <v>44.26</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="n">
-        <v>53.78</v>
+        <v>48.66</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="n">
-        <v>60.08</v>
+        <v>61.54</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -6045,11 +6045,11 @@
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr"/>
       <c r="G175" t="n">
-        <v>40.74</v>
+        <v>38.96</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -6077,7 +6077,7 @@
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="n">
-        <v>43.74</v>
+        <v>44.17</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -6109,11 +6109,11 @@
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="n">
-        <v>62.23</v>
+        <v>54.73</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -6141,7 +6141,7 @@
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="n">
-        <v>49.1</v>
+        <v>49.74</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="n">
-        <v>46.52</v>
+        <v>45.51</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="n">
-        <v>51.12</v>
+        <v>48.07</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="n">
-        <v>46.59</v>
+        <v>42.69</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="n">
-        <v>58.35</v>
+        <v>54.29</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr"/>
       <c r="G183" t="n">
-        <v>75.59999999999999</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="n">
-        <v>51.66</v>
+        <v>50.14</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="n">
-        <v>62.53</v>
+        <v>62.42</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="n">
-        <v>49.45</v>
+        <v>49.6</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="n">
-        <v>48.6</v>
+        <v>42.9</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="n">
-        <v>53.99</v>
+        <v>52.17</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -6493,11 +6493,11 @@
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="n">
-        <v>48.12</v>
+        <v>61.74</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &gt; 60</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -6525,11 +6525,11 @@
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="n">
-        <v>60.05</v>
+        <v>58.22</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -6557,7 +6557,7 @@
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="n">
-        <v>49.62</v>
+        <v>47.81</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="n">
-        <v>51.02</v>
+        <v>47.5</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="n">
-        <v>75.2</v>
+        <v>74.34</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="n">
-        <v>51.71</v>
+        <v>48.05</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="n">
-        <v>46.35</v>
+        <v>43.82</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="n">
-        <v>73.87</v>
+        <v>70.31</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="n">
-        <v>41.29</v>
+        <v>43.97</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="n">
-        <v>38.3</v>
+        <v>34.58</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="n">
-        <v>51.52</v>
+        <v>49.63</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="n">
-        <v>34.06</v>
+        <v>37.65</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="n">
-        <v>54.01</v>
+        <v>54.45</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -6909,11 +6909,11 @@
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="n">
-        <v>42.06</v>
+        <v>37.51</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -6941,7 +6941,7 @@
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr"/>
       <c r="G203" t="n">
-        <v>71.23</v>
+        <v>68.17</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr"/>
       <c r="G204" t="n">
-        <v>53.3</v>
+        <v>47.23</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="n">
-        <v>59.8</v>
+        <v>56.5</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="n">
-        <v>52.57</v>
+        <v>50.83</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -7069,11 +7069,11 @@
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="n">
-        <v>61.24</v>
+        <v>56.31</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -7101,11 +7101,11 @@
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="n">
-        <v>60.38</v>
+        <v>53.85</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -7133,11 +7133,11 @@
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="n">
-        <v>67.77</v>
+        <v>59.75</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>RSI &gt; 60</t>
+          <t>RSI 40–60</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -7165,7 +7165,7 @@
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="n">
-        <v>34.08</v>
+        <v>32.96</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -7197,11 +7197,11 @@
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="n">
-        <v>40.5</v>
+        <v>36.88</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>RSI 40–60</t>
+          <t>RSI &lt; 40</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -7229,7 +7229,7 @@
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr"/>
       <c r="G212" t="n">
-        <v>47.78</v>
+        <v>42.11</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr"/>
       <c r="G213" t="n">
-        <v>48.92</v>
+        <v>45.93</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="n">
-        <v>54.36</v>
+        <v>51.28</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr"/>
       <c r="G215" t="n">
-        <v>44.25</v>
+        <v>48</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="n">
-        <v>66.19</v>
+        <v>67.14</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="n">
-        <v>55.47</v>
+        <v>58.13</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -7572,7 +7572,11 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -7624,11 +7628,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Bullish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -7654,11 +7654,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Bearish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -7814,11 +7810,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Bullish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -7870,11 +7862,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Bearish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -8034,11 +8022,7 @@
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Bullish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -8402,7 +8386,11 @@
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
@@ -8610,7 +8598,11 @@
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
@@ -8688,11 +8680,7 @@
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Bullish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
@@ -8744,7 +8732,11 @@
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
@@ -8796,7 +8788,11 @@
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
@@ -8930,7 +8926,11 @@
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
@@ -8956,11 +8956,7 @@
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Bullish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
@@ -9012,7 +9008,11 @@
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
@@ -9038,11 +9038,7 @@
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Bullish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
@@ -9068,11 +9064,7 @@
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Bearish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
@@ -9098,11 +9090,7 @@
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Bearish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
@@ -9128,7 +9116,11 @@
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
@@ -9232,7 +9224,11 @@
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
@@ -9678,7 +9674,11 @@
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
@@ -9704,7 +9704,11 @@
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
@@ -9990,11 +9994,7 @@
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Bearish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
@@ -10098,11 +10098,7 @@
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Bearish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
@@ -10180,7 +10176,11 @@
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
@@ -10500,7 +10500,11 @@
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
@@ -10604,11 +10608,7 @@
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Bullish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
@@ -10738,11 +10738,7 @@
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Bullish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
@@ -10768,11 +10764,7 @@
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Bullish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
@@ -10958,7 +10950,11 @@
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
@@ -11036,11 +11032,7 @@
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Bullish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
@@ -11144,11 +11136,7 @@
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Bullish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
@@ -11330,7 +11318,11 @@
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr"/>
@@ -11356,7 +11348,11 @@
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr"/>
@@ -11512,7 +11508,11 @@
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr"/>
@@ -11590,11 +11590,7 @@
       </c>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Bearish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr"/>
@@ -11724,7 +11720,11 @@
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr"/>
@@ -11750,7 +11750,11 @@
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr"/>
@@ -11776,7 +11780,11 @@
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr"/>
-      <c r="E163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr"/>
@@ -11802,7 +11810,11 @@
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr"/>
@@ -11854,7 +11866,11 @@
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr"/>
@@ -11906,11 +11922,7 @@
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Bullish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
@@ -11962,11 +11974,7 @@
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Bullish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr"/>
@@ -12018,7 +12026,11 @@
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
@@ -12044,7 +12056,11 @@
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr"/>
@@ -12230,7 +12246,11 @@
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr"/>
@@ -12282,7 +12302,11 @@
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
@@ -12550,11 +12574,7 @@
       </c>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>Bullish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
@@ -12632,11 +12652,7 @@
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>Bearish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr"/>
@@ -12688,7 +12704,11 @@
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr"/>
-      <c r="E197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr"/>
@@ -12740,11 +12760,7 @@
       </c>
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr"/>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>Bullish EMA Pullback</t>
-        </is>
-      </c>
+      <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr"/>
@@ -12796,7 +12812,11 @@
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr"/>
-      <c r="E201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr"/>
@@ -12874,7 +12894,11 @@
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr"/>
-      <c r="E204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Bearish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr"/>
@@ -12978,7 +13002,11 @@
       </c>
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Bullish EMA Pullback</t>
+        </is>
+      </c>
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr"/>
@@ -13654,11 +13682,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -14008,11 +14032,7 @@
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Bearish Confluence</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -14296,11 +14316,7 @@
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
@@ -14434,7 +14450,11 @@
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
@@ -14490,11 +14510,7 @@
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Bearish Confluence</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
@@ -14732,11 +14748,7 @@
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
@@ -15266,11 +15278,7 @@
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Bearish Confluence</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
@@ -15550,11 +15558,7 @@
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
@@ -15610,7 +15614,11 @@
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
@@ -15852,11 +15860,7 @@
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
@@ -15938,11 +15942,7 @@
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Bearish Confluence</t>
-        </is>
-      </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
@@ -16378,11 +16378,7 @@
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
@@ -16460,7 +16456,11 @@
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
@@ -16538,7 +16538,11 @@
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
@@ -16986,11 +16990,7 @@
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
@@ -17042,7 +17042,11 @@
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr"/>
@@ -17438,11 +17442,7 @@
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
@@ -17498,11 +17498,7 @@
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
@@ -17632,7 +17628,11 @@
       </c>
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr"/>
@@ -17826,7 +17826,11 @@
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr"/>
@@ -17852,11 +17856,7 @@
       </c>
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Bearish Confluence</t>
-        </is>
-      </c>
+      <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr"/>
@@ -17990,11 +17990,7 @@
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr"/>
@@ -18046,11 +18042,7 @@
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Bearish Confluence</t>
-        </is>
-      </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
@@ -18508,7 +18500,11 @@
       </c>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr"/>
-      <c r="E189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
@@ -18534,7 +18530,11 @@
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Bullish Confluence</t>
+        </is>
+      </c>
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
@@ -18922,7 +18922,11 @@
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr"/>
-      <c r="E204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Bearish Confluence</t>
+        </is>
+      </c>
       <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr"/>
@@ -19000,11 +19004,7 @@
       </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr"/>
@@ -19198,11 +19198,7 @@
       </c>
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr"/>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>Bullish Confluence</t>
-        </is>
-      </c>
+      <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr"/>
@@ -19376,7 +19372,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -19395,7 +19391,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AM&amp;M</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABHARTIARTL</t>
         </is>
       </c>
     </row>
@@ -19410,7 +19406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19478,7 +19474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PIIND</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -19497,14 +19493,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APIIND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APOLICYBZR</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>WAAREEENER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -19523,7 +19519,85 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABEL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AWAAREEENER</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHDFCLIFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APETRONET</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIOC</t>
         </is>
       </c>
     </row>
@@ -19888,7 +19962,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LTM</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -19911,14 +19985,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALTM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AULTRACEMCO</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LTF</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -19941,14 +20015,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALTF</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABLUESTARCO</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BAJAJ_AUTO</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -19971,14 +20045,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABAJAJ_AUTO</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASBICARD</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -20001,14 +20075,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AVOLTAS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADIVISLAB</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -20031,14 +20105,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AICICIGI</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AALKEM</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>BAJAJ_AUTO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -20061,7 +20135,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADMART</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABAJAJ_AUTO</t>
         </is>
       </c>
     </row>
@@ -20170,7 +20244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20238,7 +20312,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -20257,14 +20331,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANATIONALUM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AETERNAL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -20283,19 +20357,19 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGMRAIRPORT</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABHARTIARTL</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -20309,19 +20383,19 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHCLTECH</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAXISBANK</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>CROMPTON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -20335,14 +20409,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AFEDERALBNK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACROMPTON</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -20361,14 +20435,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMOTHERSON</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASIEMENS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -20387,14 +20461,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACOALINDIA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASOLARINDS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -20413,19 +20487,19 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AASHOKLEY</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATASTEEL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>ICICIPRULI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -20439,14 +20513,14 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATVSMOTOR</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AICICIPRULI</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -20465,14 +20539,14 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADIVISLAB</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAPOLLOHOSP</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -20491,19 +20565,19 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASHRIRAMFIN</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIENSOL</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>LTM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -20517,14 +20591,14 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABAJAJHLDNG</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALTM</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -20543,14 +20617,14 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APGEL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AALKEM</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -20569,14 +20643,14 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABHARATFORG</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AUNITDSPR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BAJAJ_AUTO</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -20595,14 +20669,14 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABAJAJ_AUTO</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASUNPHARMA</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -20621,14 +20695,14 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINFY</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHAVELLS</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -20647,7 +20721,137 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIOC</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APOWERINDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>KFINTECH</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKFINTECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJINDALSTEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAMBER</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASONACOMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMANKIND</t>
         </is>
       </c>
     </row>
@@ -20662,7 +20866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L210"/>
+  <dimension ref="A1:L215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20834,7 +21038,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -20853,14 +21057,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AOIL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGAIL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -20879,14 +21083,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGAIL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANATIONALUM</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -20905,14 +21109,14 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANATIONALUM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAUROPHARMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -20931,14 +21135,14 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAUROPHARMA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AOFSS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -20957,14 +21161,14 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AOFSS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJSWSTEEL</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -20983,14 +21187,14 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJSWSTEEL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMOTILALOFS</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -21009,14 +21213,14 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMOTILALOFS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINDUSINDBK</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -21035,14 +21239,14 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINDUSINDBK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHDFCAMC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -21061,14 +21265,14 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHDFCAMC</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAMBUJACEM</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -21087,14 +21291,14 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAMBUJACEM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACOLPAL</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -21113,14 +21317,14 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACOLPAL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGODREJPROP</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -21139,14 +21343,14 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGODREJPROP</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHYUNDAI</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -21165,14 +21369,14 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHYUNDAI</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGMRAIRPORT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -21191,14 +21395,14 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGMRAIRPORT</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMAZDOCK</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -21217,14 +21421,14 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMAZDOCK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHCLTECH</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -21243,14 +21447,14 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHCLTECH</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AANGELONE</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -21269,7 +21473,7 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AANGELONE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AASIANPAINT</t>
         </is>
       </c>
     </row>
@@ -21588,7 +21792,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -21607,14 +21811,14 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABOSCHLTD</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGODREJCP</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -21633,14 +21837,14 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATAPOWER</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABOSCHLTD</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -21659,14 +21863,14 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIDFCFIRSTB</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATAPOWER</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -21685,14 +21889,14 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AULTRACEMCO</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIDFCFIRSTB</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -21711,14 +21915,14 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIRFC</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AULTRACEMCO</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -21737,14 +21941,14 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AASHOKLEY</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIRFC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -21763,14 +21967,14 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASIEMENS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AASHOKLEY</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TATAELXSI</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -21789,14 +21993,14 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATAELXSI</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASIEMENS</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>INOXWIND</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -21815,14 +22019,14 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINOXWIND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATAELXSI</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TATAMOTORS</t>
+          <t>INOXWIND</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -21841,14 +22045,14 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATAMOTORS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINOXWIND</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>TATAMOTORS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -21867,14 +22071,14 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMAXHEALTH</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATAMOTORS</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -21893,14 +22097,14 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIENT</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMAXHEALTH</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>JUBLFOOD</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -21919,14 +22123,14 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJUBLFOOD</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIENT</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SUZLON</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21945,14 +22149,14 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASUZLON</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJUBLFOOD</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21971,14 +22175,14 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPORTS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASUZLON</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21997,14 +22201,14 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASOLARINDS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPORTS</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22023,14 +22227,14 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABCAPITAL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASOLARINDS</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>IREDA</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22049,14 +22253,14 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIREDA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABCAPITAL</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>KALYANKJIL</t>
+          <t>IREDA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -22075,14 +22279,14 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKALYANKJIL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIREDA</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>KALYANKJIL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -22101,14 +22305,14 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACHOLAFIN</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKALYANKJIL</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -22127,14 +22331,14 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APIDILITIND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACHOLAFIN</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -22153,14 +22357,14 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHDFCBANK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APIDILITIND</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -22179,14 +22383,14 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHEROMOTOCO</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHDFCBANK</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -22205,14 +22409,14 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASBIN</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHEROMOTOCO</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>VMM</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -22231,14 +22435,14 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AVMM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASBIN</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>VMM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -22257,14 +22461,14 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APOLICYBZR</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AVMM</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -22283,14 +22487,14 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AWIPRO</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APOLICYBZR</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -22309,14 +22513,14 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIGREEN</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AWIPRO</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -22335,14 +22539,14 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATASTEEL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIGREEN</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PREMIERENE</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -22361,14 +22565,14 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APREMIERENE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATASTEEL</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>PREMIERENE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -22387,14 +22591,14 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPOWER</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APREMIERENE</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -22413,14 +22617,14 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APAYTM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPOWER</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -22439,14 +22643,14 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMPHASIS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APAYTM</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -22465,14 +22669,14 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKPITTECH</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMPHASIS</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -22491,14 +22695,14 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALICHSGFIN</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKPITTECH</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -22517,14 +22721,14 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASAIL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALICHSGFIN</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -22543,14 +22747,14 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AOBEROIRLTY</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASAIL</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CNXMIDCAP</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -22569,14 +22773,14 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACNXMIDCAP</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AOBEROIRLTY</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>CNXMIDCAP</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -22595,14 +22799,14 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINDIANB</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACNXMIDCAP</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -22621,14 +22825,14 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AICICIPRULI</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHINDZINC</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PIIND</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -22647,14 +22851,14 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APIIND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINDIANB</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GODFRYPHLP</t>
+          <t>ICICIPRULI</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -22673,14 +22877,14 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGODFRYPHLP</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AICICIPRULI</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>PIIND</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -22699,14 +22903,14 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABLUESTARCO</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APIIND</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>GODFRYPHLP</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -22725,14 +22929,14 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APFC</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGODFRYPHLP</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -22751,14 +22955,14 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABAJFINANCE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABLUESTARCO</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -22777,14 +22981,14 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHINDUNILVR</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APFC</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BANKINDIA</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -22803,14 +23007,14 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABANKINDIA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABAJFINANCE</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -22829,14 +23033,14 @@
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAPLAPOLLO</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHINDUNILVR</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>WAAREEENER</t>
+          <t>BANKINDIA</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -22855,14 +23059,14 @@
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AWAAREEENER</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABANKINDIA</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -22881,14 +23085,14 @@
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADRREDDY</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAPLAPOLLO</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>WAAREEENER</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -22907,14 +23111,14 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAPOLLOHOSP</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AWAAREEENER</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -22933,14 +23137,14 @@
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AUPL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADRREDDY</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -22959,14 +23163,14 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMARUTI</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAPOLLOHOSP</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>UPL</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -22985,14 +23189,14 @@
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASBICARD</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AUPL</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -23011,14 +23215,14 @@
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIEX</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMARUTI</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -23037,14 +23241,14 @@
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINDHOTEL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASBICARD</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BDL</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -23063,14 +23267,14 @@
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABDL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIEX</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -23089,14 +23293,14 @@
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACDSL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINDHOTEL</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>BDL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -23115,14 +23319,14 @@
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACONCOR</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABDL</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -23141,14 +23345,14 @@
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATACONSUM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACDSL</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -23167,14 +23371,14 @@
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATVSMOTOR</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACONCOR</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -23193,14 +23397,14 @@
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AICICIBANK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATACONSUM</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -23219,14 +23423,14 @@
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASUPREMEIND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATVSMOTOR</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -23245,14 +23449,14 @@
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADIXON</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AICICIBANK</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -23271,14 +23475,14 @@
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATECHM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASUPREMEIND</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CNXFINANCE</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -23297,14 +23501,14 @@
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACNXFINANCE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADIXON</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -23323,14 +23527,14 @@
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACUMMINSIND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATECHM</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>CNXFINANCE</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -23349,14 +23553,14 @@
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASRF</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACNXFINANCE</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -23375,14 +23579,14 @@
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATITAN</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACUMMINSIND</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>SRF</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -23401,14 +23605,14 @@
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APERSISTENT</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASRF</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -23427,14 +23631,14 @@
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APOWERGRID</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATITAN</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -23453,14 +23657,14 @@
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADIVISLAB</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APERSISTENT</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -23479,14 +23683,14 @@
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATIINDIA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APOWERGRID</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -23505,14 +23709,14 @@
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIENSOL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADIVISLAB</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -23531,14 +23735,14 @@
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANIFTY</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATIINDIA</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SWIGGY</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -23557,14 +23761,14 @@
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASWIGGY</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIENSOL</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>PAGEIND</t>
+          <t>NIFTY</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -23583,14 +23787,14 @@
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APAGEIND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANIFTY</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>SWIGGY</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -23609,14 +23813,14 @@
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APNB</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASWIGGY</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>LTM</t>
+          <t>PAGEIND</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -23635,14 +23839,14 @@
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALTM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APAGEIND</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -23661,14 +23865,14 @@
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIDEA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APNB</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>FORCEMOT</t>
+          <t>LTM</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -23687,14 +23891,14 @@
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AFORCEMOT</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALTM</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -23713,14 +23917,14 @@
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASHRIRAMFIN</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIDEA</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>FORCEMOT</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -23739,14 +23943,14 @@
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AVBL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AFORCEMOT</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -23765,14 +23969,14 @@
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AEXIDEIND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASHRIRAMFIN</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -23791,14 +23995,14 @@
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABAJAJFINSV</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AVBL</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>LTF</t>
+          <t>EXIDEIND</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -23817,14 +24021,14 @@
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALTF</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AEXIDEIND</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -23843,14 +24047,14 @@
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACAMS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABAJAJFINSV</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>LTF</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -23869,14 +24073,14 @@
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AFORTIS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALTF</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -23895,14 +24099,14 @@
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AZYDUSLIFE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACAMS</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>COCHINSHIP</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -23921,14 +24125,14 @@
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACOCHINSHIP</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINDIGO</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>NAM_INDIA</t>
+          <t>FORTIS</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -23947,14 +24151,14 @@
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANAM_INDIA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AFORTIS</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -23973,14 +24177,14 @@
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABEL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AZYDUSLIFE</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>COCHINSHIP</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -23999,14 +24203,14 @@
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADLF</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACOCHINSHIP</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>NAM_INDIA</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -24025,14 +24229,14 @@
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AALKEM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANAM_INDIA</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -24051,14 +24255,14 @@
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABSE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABEL</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -24077,14 +24281,14 @@
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AUNITDSPR</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADLF</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -24103,14 +24307,14 @@
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABAJAJHLDNG</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AALKEM</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -24129,14 +24333,14 @@
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALT</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABSE</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -24155,14 +24359,14 @@
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AEICHERMOT</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AUNITDSPR</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -24181,14 +24385,14 @@
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APGEL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABAJAJHLDNG</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -24207,14 +24411,14 @@
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABHEL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALT</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -24233,14 +24437,14 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABHARATFORG</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AEICHERMOT</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -24259,14 +24463,14 @@
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALAURUSLABS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APGEL</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -24285,14 +24489,14 @@
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASUNPHARMA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABHEL</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -24311,14 +24515,14 @@
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APRESTIGE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABHARATFORG</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -24337,14 +24541,14 @@
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AUNIONBANK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALAURUSLABS</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -24363,14 +24567,14 @@
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACOFORGE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASUNPHARMA</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -24389,14 +24593,14 @@
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHDFCLIFE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APRESTIGE</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BANKNIFTY</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -24415,14 +24619,14 @@
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABANKNIFTY</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AUNIONBANK</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -24441,14 +24645,14 @@
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATORNTPHARM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACOFORGE</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -24467,14 +24671,14 @@
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ARADICO</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHDFCLIFE</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>BANKNIFTY</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -24493,14 +24697,14 @@
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANESTLEIND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABANKNIFTY</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -24519,14 +24723,14 @@
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AASTRAL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATORNTPHARM</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -24545,14 +24749,14 @@
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAUBANK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ARADICO</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -24571,14 +24775,14 @@
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APOLYCAB</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANESTLEIND</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -24597,14 +24801,14 @@
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ARECLTD</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AASTRAL</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -24623,14 +24827,14 @@
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACGPOWER</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAUBANK</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -24649,14 +24853,14 @@
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHAVELLS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APOLYCAB</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -24675,14 +24879,14 @@
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABANDHANBNK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ARECLTD</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -24701,14 +24905,14 @@
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMARICO</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACGPOWER</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -24727,14 +24931,14 @@
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AVEDL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHAVELLS</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>POWERINDIA</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -24753,14 +24957,14 @@
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APOWERINDIA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABANDHANBNK</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -24779,14 +24983,14 @@
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACANBK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMARICO</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -24805,14 +25009,14 @@
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACIPLA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AVEDL</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -24831,14 +25035,14 @@
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMANAPPURAM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APOWERINDIA</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -24857,14 +25061,14 @@
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AM&amp;M</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACANBK</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -24883,14 +25087,14 @@
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANTPC</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACIPLA</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -24909,14 +25113,14 @@
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMFSL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMANAPPURAM</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -24935,14 +25139,14 @@
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINDUSTOWER</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AM&amp;M</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>BAJAJ_AUTO</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -24961,14 +25165,14 @@
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABAJAJ_AUTO</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANTPC</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>GVT&amp;D</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -24987,14 +25191,14 @@
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGVT&amp;D</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMFSL</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -25013,14 +25217,14 @@
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A360ONE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINDUSTOWER</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>BAJAJ_AUTO</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -25039,14 +25243,14 @@
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJSWENERGY</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABAJAJ_AUTO</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -25065,14 +25269,14 @@
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABRITANNIA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGVT&amp;D</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -25091,14 +25295,14 @@
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AVOLTAS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A360ONE</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -25117,14 +25321,14 @@
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATRENT</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJSWENERGY</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>KEI</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -25143,14 +25347,14 @@
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKEI</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANMDC</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -25169,14 +25373,14 @@
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKFINTECH</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABRITANNIA</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -25195,14 +25399,14 @@
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AONGC</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AVOLTAS</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -25221,14 +25425,14 @@
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ARELIANCE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATRENT</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>KEI</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -25247,14 +25451,14 @@
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADABUR</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKEI</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -25273,14 +25477,14 @@
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKOTAKBANK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKFINTECH</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -25299,14 +25503,14 @@
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AUNOMINDA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AONGC</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -25325,14 +25529,14 @@
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANYKAA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ARELIANCE</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>KAYNES</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -25351,14 +25555,14 @@
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKAYNES</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADABUR</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -25377,14 +25581,14 @@
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADELHIVERY</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKOTAKBANK</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -25403,14 +25607,14 @@
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AICICIGI</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AUNOMINDA</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>NBCC</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -25429,14 +25633,14 @@
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANBCC</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANYKAA</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>NIFTYJR</t>
+          <t>KAYNES</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -25455,14 +25659,14 @@
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANIFTYJR</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKAYNES</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -25481,14 +25685,14 @@
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABIOCON</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADELHIVERY</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -25507,14 +25711,14 @@
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ARBLBANK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AICICIGI</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>YESBANK</t>
+          <t>NBCC</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -25533,14 +25737,14 @@
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AYESBANK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANBCC</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>NIFTYJR</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -25559,14 +25763,14 @@
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APETRONET</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANIFTYJR</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -25585,14 +25789,14 @@
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANAUKRI</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ARBLBANK</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>YESBANK</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -25611,14 +25815,14 @@
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGRASIM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AYESBANK</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -25637,14 +25841,14 @@
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMUTHOOTFIN</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APETRONET</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -25663,14 +25867,14 @@
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APHOENIXLTD</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANAUKRI</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -25689,14 +25893,14 @@
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHINDALCO</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGRASIM</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -25715,14 +25919,14 @@
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABPCL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMUTHOOTFIN</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -25741,14 +25945,14 @@
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJINDALSTEL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APHOENIXLTD</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -25767,14 +25971,14 @@
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAMBER</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHINDALCO</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>TMPV</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -25793,14 +25997,14 @@
       <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATMPV</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADMART</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -25819,14 +26023,14 @@
       <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASONACOMS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABPCL</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -25845,14 +26049,14 @@
       <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJIOFIN</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJINDALSTEL</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -25871,14 +26075,14 @@
       <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASBILIFE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAMBER</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>TMPV</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -25897,14 +26101,14 @@
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINFY</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATMPV</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -25923,14 +26127,14 @@
       <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALICI</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASONACOMS</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -25949,14 +26153,14 @@
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHAL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJIOFIN</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -25975,14 +26179,14 @@
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APNBHOUSING</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASBILIFE</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -26001,14 +26205,14 @@
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APATANJALI</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINFY</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>RVNL</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -26027,14 +26231,14 @@
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ARVNL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALICI</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -26053,14 +26257,14 @@
       <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIOC</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHAL</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -26079,14 +26283,14 @@
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANHPC</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APNBHOUSING</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>PATANJALI</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -26105,14 +26309,14 @@
       <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABB</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APATANJALI</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>NUVAMA</t>
+          <t>RVNL</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -26131,14 +26335,14 @@
       <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANUVAMA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ARVNL</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -26156,6 +26360,136 @@
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>HINDPETRO</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHINDPETRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>NHPC</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANHPC</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABB</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr"/>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANUVAMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr">
         <is>
           <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMANKIND</t>
         </is>
@@ -32002,7 +32336,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -32032,7 +32366,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -32242,7 +32576,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bullish Reversal Watch</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -32272,7 +32606,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -32302,7 +32636,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -32332,7 +32666,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -32422,7 +32756,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bullish Reversal Watch</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -32452,7 +32786,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bullish Reversal Watch</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -32692,7 +33026,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Bearish Reversal Watch</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -32872,7 +33206,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -32992,7 +33326,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -33172,7 +33506,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -33202,7 +33536,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Bearish Reversal Watch</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -33352,7 +33686,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Weak Bearish</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -33442,7 +33776,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Weak Bullish</t>
+          <t>Bullish Reversal Watch</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -33472,7 +33806,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -33652,7 +33986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Weak Bearish</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -33742,7 +34076,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -33892,7 +34226,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -34042,7 +34376,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Bearish Reversal Watch</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -34072,7 +34406,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -34192,7 +34526,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -34342,7 +34676,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -34402,7 +34736,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -34432,7 +34766,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Weak Bearish</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -34462,7 +34796,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -34522,7 +34856,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Weak Bullish</t>
+          <t>Bullish Reversal Watch</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -34612,7 +34946,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -34672,7 +35006,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -34762,7 +35096,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Bearish Reversal Watch</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -34822,7 +35156,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -35062,7 +35396,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -35092,7 +35426,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -35242,7 +35576,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -35272,7 +35606,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -35422,7 +35756,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Weak Bearish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -35512,7 +35846,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -35542,7 +35876,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -35602,7 +35936,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Weak Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -35662,7 +35996,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Weak Bullish</t>
+          <t>Bullish Reversal Watch</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -35812,7 +36146,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -35902,7 +36236,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -35932,7 +36266,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bullish Reversal Watch</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -36172,7 +36506,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -36262,7 +36596,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -36382,7 +36716,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -36412,7 +36746,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -36442,7 +36776,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -36472,7 +36806,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -36592,7 +36926,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Bullish Reversal Watch</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -36682,7 +37016,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -36712,7 +37046,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Weak Bearish</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -36802,7 +37136,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -36832,7 +37166,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Bearish Reversal Watch</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -36982,7 +37316,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -37042,7 +37376,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Bearish Reversal Watch</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -37072,7 +37406,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -37102,7 +37436,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -37252,7 +37586,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Weak Bearish</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -37312,7 +37646,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -37342,7 +37676,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -37372,7 +37706,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
@@ -37492,7 +37826,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -37552,7 +37886,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -37582,7 +37916,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Bullish Reversal Watch</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -37642,7 +37976,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Bullish Reversal Watch</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -37732,7 +38066,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Weak Bearish</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -37912,7 +38246,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Strong Bullish</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -37942,7 +38276,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -37972,7 +38306,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -38002,7 +38336,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -38092,7 +38426,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -38122,7 +38456,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -38152,7 +38486,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Strong Bullish</t>
+          <t>Bullish Cooling</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -38212,7 +38546,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Bearish Reversal Watch</t>
+          <t>Weak Bearish</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -38242,7 +38576,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Bearish Recovery Attempt</t>
+          <t>Strong Bearish</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -38302,7 +38636,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Bullish Cooling</t>
+          <t>Weak Bullish</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -38332,7 +38666,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Strong Bearish</t>
+          <t>Bearish Recovery Attempt</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -38525,7 +38859,11 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -38759,7 +39097,11 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -39127,7 +39469,11 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -39265,7 +39611,11 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -39473,7 +39823,11 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
@@ -39577,7 +39931,11 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
@@ -40099,11 +40457,7 @@
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -40479,11 +40833,7 @@
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
+      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
@@ -40777,11 +41127,7 @@
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
@@ -41365,11 +41711,7 @@
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
@@ -41395,7 +41737,11 @@
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
@@ -42333,7 +42679,11 @@
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
@@ -42541,11 +42891,7 @@
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
@@ -42679,11 +43025,7 @@
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
@@ -43163,7 +43505,11 @@
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
@@ -43501,7 +43847,11 @@
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
@@ -43527,7 +43877,11 @@
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
@@ -44241,11 +44595,7 @@
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr"/>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
+      <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr"/>
       <c r="I217" t="inlineStr"/>
@@ -46182,7 +46532,11 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Strong Downtrend</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
@@ -48260,11 +48614,7 @@
           <t>Uptrend/Downtrend</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Strong Uptrend</t>
-        </is>
-      </c>
+      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
